--- a/docs/oc-top-proveedores/endoprotesis-ortopedia-y-trauma.xlsx
+++ b/docs/oc-top-proveedores/endoprotesis-ortopedia-y-trauma.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="endoprotesis-ort top prov" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="endoprotesis-ort top prov" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17080,7 +17080,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17812,7 +17812,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">

--- a/docs/oc-top-proveedores/endoprotesis-ortopedia-y-trauma.xlsx
+++ b/docs/oc-top-proveedores/endoprotesis-ortopedia-y-trauma.xlsx
@@ -745,7 +745,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +993,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1180,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1855,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2286,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2900,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +2965,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3091,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3583,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5356,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5543,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +5913,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7076,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7385,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8060,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8430,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8495,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +9963,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10028,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10337,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10646,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11138,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11508,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +11573,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +11699,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13045,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13232,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +13541,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +13972,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14342,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14468,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +14716,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +15696,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17042,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17229,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +17477,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +17969,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +19559,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +19685,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +19994,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20120,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +20246,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +20372,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +20437,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +20563,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +20689,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +20876,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +21551,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +21921,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +21986,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +22112,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +22543,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +22974,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +23405,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +23592,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
